--- a/performance_review/구성원_배포용/자가점검표_김영희.xlsx
+++ b/performance_review/구성원_배포용/자가점검표_김영희.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -515,43 +515,50 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. 숫자로 입력하는 항목(기여도, 성과도, AI 자가점수 등)은 1~10 사이의 정수만 입력할 수 있습니다.</t>
+          <t xml:space="preserve">  2. 모든 항목은 '정량 목표 → 달성 결과 → 자가평가 점수(1~10)' 3단 구조입니다. 목표와 결과에는 가능한 숫자(%, 건수, 일수, 시간 등)를 포함해 적어주세요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. 동료평가(Peer) 항목에는 본인 파트에서 1명, 타 파트에서 1명을 추천 이름과 사유를 함께 적어주세요.</t>
+          <t xml:space="preserve">  3. 점수 칸은 1~10 사이의 정수만 입력할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. 작성이 끝나면 이 파일을 저장한 뒤 담당자(팀장/HR)에게 회신해 주세요. 담당자가 마스터 워크북에 반영합니다.</t>
+          <t xml:space="preserve">  4. 동료평가(Peer) 항목에는 본인 파트에서 1명, 타 파트에서 1명을 추천 이름과 사유를 함께 적어주세요.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. 작성이 끝나면 이 파일을 저장한 뒤 담당자(팀장/HR)에게 회신해 주세요. 담당자가 마스터 워크북에 반영하거나, 여러 명의 파일을 모아 ranking_dashboard.html에 그대로 업로드해 통계를 볼 수 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>참고</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 이 파일의 입력 내용은 팀장 정성평가와 동료 추천 집계를 거쳐 성과 60% · 역량 20% · 동료평가 20% 가중치로 최종 점수에 반영됩니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 이 파일의 정량 항목만으로 성과 60% · 역량 20% · 동료평가 20% 가중치로 최종 점수가 자동 계산됩니다 (별도 팀장 정성평가 점수 불필요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - 완전 오프라인 파일이며, 회신 전까지 본인 PC에만 저장됩니다.</t>
         </is>
@@ -568,10 +575,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -581,7 +588,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>구성원 성과 자가점검표</t>
+          <t>구성원 성과 자가점검표 (정량 목표 기반)</t>
         </is>
       </c>
     </row>
@@ -636,278 +643,405 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ⅰ. 성과 (What)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>Ⅰ. 성과 (What) — 정량 목표 → 달성 결과 → 자가평가 점수(1~10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>중점과제 1순위 - 과제명</t>
+          <t>중점과제 1순위 — 과제명 및 정량 목표</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>품질 이슈 Root Cause 분석 체계 구축</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>품질 이슈 Root Cause 분석체계 구축 — 목표: 분석 리드타임 30% 단축</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>중점과제 1순위 - 목표 및 결과</t>
+          <t>달성 결과 (정량)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>분석 리드타임 40% 단축, 재발률 20%p 감소</t>
+          <t>리드타임 40% 단축, 재발률 20%p 감소</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>중점과제 2순위 - 과제명</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>협력사 품질 감사 프로세스 개선</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>자가평가 점수 (1~10)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>중점과제 2순위 - 목표 및 결과</t>
+          <t>중점과제 2순위 — 과제명 및 정량 목표</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>감사 항목 표준화로 감사 소요일 3일-&gt;1.5일</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>협력사 품질 감사 프로세스 개선 — 목표: 감사 소요일 2일 이내</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>중점과제 3순위 - 과제명</t>
+          <t>달성 결과 (정량)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>신입 사원 OJT 프로그램 설계</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t>감사 소요일 1.5일로 단축</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>중점과제 3순위 - 목표 및 결과</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>OJT 만족도 4.6/5.0, 조기 전력화 기간 단축</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>자가평가 점수 (1~10)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>추가 과제</t>
+          <t>중점과제 3순위 — 과제명 및 정량 목표</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>품질 데이터 대시보드 구축 (부서 공용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>신입 OJT 프로그램 설계 — 목표: 만족도 4.5/5.0 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>가장 아쉬운 성과 (사유 포함)</t>
+          <t>달성 결과 (정량)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>협력사 감사 프로세스 전사 확산까지는 완료하지 못함</t>
+          <t>만족도 4.6/5.0 달성</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>내가 팀 성과에 기여한 정도 (1~10, 정량)</t>
+          <t>자가평가 점수 (1~10)</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>자신의 역할에 비추어 올해 성과도 자가평가 (1~10, 정량)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Ⅱ. 역량 (How) - 전문성 강화를 위한 노력</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+          <t>추가 과제 — 과제명 및 정량 목표</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>품질 데이터 대시보드 구축 — 목표: 부서 공용 대시보드 1건 오픈</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>달성 결과 (정량)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>대시보드 오픈, 부서 전체 사용 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>자가평가 점수 (1~10)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>전문성 강화를 위한 노력</t>
+          <t>가장 아쉬운 성과 (목표 대비 부족했던 점, 정량 포함)</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>품질 데이터 분석 전문성 강화를 위한 통계 심화 과정 수료</t>
+          <t>협력사 감사 프로세스 전사 확산(목표: 3개 부서) 대비 1개 부서만 적용</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>지식측면: SKHU 수료 학점</t>
+          <t>자가평가 점수 (1~10, 낮을수록 아쉬움이 컸음)</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>지식측면: mySuni 수료 학점</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>6</v>
+          <t>팀 기여도 — 근거 (선택)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>품질 체계 개선이 전사 지표에 직접 반영</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>AI 활용 역량 자가점수 (1~10, 정량)</t>
+          <t>내가 팀 성과에 기여한 정도 (1~10, 정량)</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>종합 성과 자가평가 — 근거 (선택)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>자신의 역할에 비추어 올해 성과도 자가평가 (1~10, 정량)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ⅱ. 역량 (How) — 정량 목표 → 달성 결과 → 자가평가 점수(1~10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>전문성 강화를 위한 노력 — 정량 목표</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>통계 심화 과정 1개 수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>달성 결과 (정량)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>과정 수료 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>자가평가 점수 (1~10)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>지식측면: SKHU 수료 학점</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>지식측면: mySuni 수료 학점</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>AI 활용 역량 — 정량 목표 (예: 월 N회 이상 활용)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>불량 예측 모델 PoC 1건 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>달성 결과 (정량)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>PoC 진행, 정확도 82% 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>자가평가 점수 (1~10)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>AI 활용 사례</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>불량 예측 모델에 AI 활용 검토, PoC 진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Ⅲ. 동료평가 (Peer) 추천 - 본인파트 1명 + 타파트 1명</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Ⅲ. 동료평가 (Peer) 추천 — 본인파트 1명 + 타파트 1명</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>본인 파트 추천 동료 - 이름</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>홍길동</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>본인 파트 추천 동료 - 추천 사유</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>공정 이슈 발생 시 근본 원인 분석을 함께 리드하며 신뢰도 높은 협업을 보여줌</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>타 파트 추천 동료 - 이름</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>이철수</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>타 파트 추천 동료 - 추천 사유</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>품질-기획 간 일정 조율에서 상호 입장을 잘 이해하고 합리적으로 조정함</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="38">
+    <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B22:E22"/>
-    <mergeCell ref="A27:E27"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B42:E42"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A38:E38"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B28:E28"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B17 B18 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="1~10 사이의 정수를 입력하세요." type="whole" operator="between">
+    <dataValidation sqref="B11 B14 B17 B20 B22 B24 B26 B31 B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="1~10 사이의 정수를 입력하세요." type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation sqref="B22 B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="0 이상의 숫자를 입력하세요." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B32 B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="0 이상의 숫자를 입력하세요." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/performance_review/구성원_배포용/자가점검표_김영희.xlsx
+++ b/performance_review/구성원_배포용/자가점검표_김영희.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -553,12 +553,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 이 파일의 정량 항목만으로 성과 60% · 역량 20% · 동료평가 20% 가중치로 최종 점수가 자동 계산됩니다 (별도 팀장 정성평가 점수 불필요).</t>
+          <t xml:space="preserve">  - 이 파일의 정량 항목만으로 성과 60% · 역량 20% · 동료평가 20% 가중치의 '자가점검 기준점수'가 자동 계산됩니다 (별도 팀장 정성평가 점수 불필요).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 담당자 검토 단계에서 팀장이 -10~+10점의 소폭 조정점수를 더할 수 있습니다(자가점수 부풀리기 방지용, 특별한 사유가 없으면 0). 이 조정은 이 개인 파일이 아니라 관리자 워크북/대시보드에서 이뤄집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - 완전 오프라인 파일이며, 회신 전까지 본인 PC에만 저장됩니다.</t>
         </is>

--- a/performance_review/구성원_배포용/자가점검표_김영희.xlsx
+++ b/performance_review/구성원_배포용/자가점검표_김영희.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -560,12 +560,19 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 담당자 검토 단계에서 팀장이 -10~+10점의 소폭 조정점수를 더할 수 있습니다(자가점수 부풀리기 방지용, 특별한 사유가 없으면 0). 이 조정은 이 개인 파일이 아니라 관리자 워크북/대시보드에서 이뤄집니다.</t>
+          <t xml:space="preserve">  - 동료평가에서 추천을 받으면(동료환산점수 20% 가중치와 별개로) 추천 1회당 +1점의 추천가산점이 상한 없이 최종점수에 더해집니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 담당자 검토 단계에서 팀장이 -10~+10점의 소폭 조정점수를 더할 수 있습니다(자가점수 부풀리기 방지용, 특별한 사유가 없으면 0). 이 조정은 이 개인 파일이 아니라 관리자 워크북/대시보드에서 이뤄집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - 완전 오프라인 파일이며, 회신 전까지 본인 PC에만 저장됩니다.</t>
         </is>
